--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -824,99 +860,99 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>QUINTA - OFERTA ESPECIAL 22/10/25</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>289794</v>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="n">
-        <v>22.99</v>
+      <c r="C16" s="8" t="n">
+        <v>119927</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>QUINTA - OFERTA ESPECIAL 22/10/25</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>104601</v>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>16.99</v>
+      <c r="C17" s="8" t="n">
+        <v>225767</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>FRANGO BONASA KG CONGELADO</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE SUINO 23/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>105461</v>
+        <v>289794</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="6" t="n">
-        <v>30.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE SUINO 23/10/25</t>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>105458</v>
+        <v>104601</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>CHAMBARI KG</t>
+          <t>SOBRECOXA DE FRANGO SADIA PCT 1KG</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="6" t="n">
-        <v>17.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="20">
@@ -931,16 +967,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>105449</v>
+        <v>105461</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>BISTECA BOVINA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="6" t="n">
-        <v>33.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="21">
@@ -955,16 +991,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>105452</v>
+        <v>105458</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>PATINHO BOVINO KG</t>
+          <t>CHAMBARI KG</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="n">
-        <v>34.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="22">
@@ -975,20 +1011,20 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>106053</v>
+        <v>105449</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>BISTECA SUINA CARRE KG</t>
+          <t>COXÃO DURO KG</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="n">
-        <v>16.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="23">
@@ -999,20 +1035,20 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>105062</v>
+        <v>105452</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>BISTECA SUINA DO PERNIL KG</t>
+          <t>PATINHO BOVINO KG</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="6" t="n">
-        <v>16.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="24">
@@ -1027,16 +1063,16 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>105433</v>
+        <v>106053</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>COSTELA SUINA KG</t>
+          <t>BISTECA SUINA CARRE KG</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="6" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="25">
@@ -1051,16 +1087,16 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>106008</v>
+        <v>105062</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>INGREDIENTES PARA FEIJOADA KG</t>
+          <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="6" t="n">
-        <v>18.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="26">
@@ -1075,16 +1111,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>106054</v>
+        <v>105433</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>LOMBO SUINO FRESCO KG</t>
+          <t>COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="6" t="n">
-        <v>18.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="27">
@@ -1099,11 +1135,11 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>258810</v>
+        <v>106008</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>PANCETA SUINA KG</t>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
@@ -1123,16 +1159,16 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>106052</v>
+        <v>106054</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>PELE SUINA KG</t>
+          <t>LOMBO SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="n">
-        <v>11.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="29">
@@ -1147,16 +1183,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>106050</v>
+        <v>258810</v>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>PÉ SUINO KG</t>
+          <t>PANCETA SUINA KG</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="n">
-        <v>9.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="30">
@@ -1171,11 +1207,11 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>106034</v>
+        <v>106052</v>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t>PELE SUINA KG</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
@@ -1195,64 +1231,64 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>106032</v>
+        <v>106050</v>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t>PÉ SUINO KG</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="n">
-        <v>18.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+          <t>QUINTA - AÇOUGUE SUINO 23/10/25</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #04 PEIXES</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>203713</v>
+        <v>106034</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>FILÉ DE TILAPIA BOUA 800G</t>
+          <t>SUAN SUINA KG</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="n">
-        <v>41.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+          <t>QUINTA - AÇOUGUE SUINO 23/10/25</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>194424</v>
+        <v>106032</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA CALABRESA BOUA 400G</t>
+          <t>TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="n">
-        <v>13.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="34">
@@ -1263,20 +1299,20 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #04 PEIXES</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>289127</v>
+        <v>203713</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
+          <t>FILÉ DE TILAPIA BOUA 800G</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="n">
-        <v>7.89</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="35">
@@ -1291,16 +1327,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>105765</v>
+        <v>194424</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
+          <t>LINGUIÇA CALABRESA BOUA 400G</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="n">
-        <v>9.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="36">
@@ -1315,16 +1351,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>105770</v>
+        <v>289127</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
+          <t>LINGUIÇA MISTA FININHA DEFUMADA SADIA 215G</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="n">
-        <v>11.7</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="37">
@@ -1339,16 +1375,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>252392</v>
+        <v>105765</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
+          <t xml:space="preserve">MORTADELA PERDIGAO KG MISTA </t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="n">
-        <v>15.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="38">
@@ -1363,15 +1399,63 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>173481</v>
+        <v>105770</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>SALAME ITALIANO SEARA 100G FATIADO</t>
+          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="6" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>252392</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>PEITO DE PERU SADIA 200G DEFUMADO FATIAS FINAS</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="6" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/QUINTA - PERECIVEIS 22 E 23/10/25</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>173481</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>SALAME ITALIANO SEARA 100G FATIADO</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="n">
         <v>10.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,26 +58,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0045A045"/>
-        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -133,18 +109,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -876,98 +840,98 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="3" t="n">
         <v>105457</v>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>CARNE BOVINA SERENADA KG</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr"/>
-      <c r="F16" s="10" t="n">
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="n">
         <v>33.99</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="3" t="n">
         <v>105458</v>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>CHAMBARI KG</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="10" t="n">
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="n">
         <v>17.99</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="3" t="n">
         <v>105471</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>COSTELA BOVINA KG</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="10" t="n">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="n">
         <v>18.99</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="3" t="n">
         <v>105449</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>COXÃO DURO KG</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="10" t="n">
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="n">
         <v>34.99</v>
       </c>
     </row>
@@ -996,74 +960,74 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="3" t="n">
         <v>105062</v>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>BISTECA SUINA DO PERNIL KG</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="10" t="n">
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
         <v>17.99</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="3" t="n">
         <v>106054</v>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>LOMBO SUINO FRESCO KG</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="10" t="n">
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="n">
         <v>17.99</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="3" t="n">
         <v>258810</v>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>PANCETA SUINA KG</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="10" t="n">
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="n">
         <v>16.99</v>
       </c>
     </row>
@@ -1092,74 +1056,74 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="3" t="n">
         <v>106050</v>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>PÉ SUINO KG</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="10" t="n">
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="n">
         <v>8.99</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="3" t="n">
         <v>106034</v>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>SUAN SUINA KG</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="10" t="n">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
         <v>10.99</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>QUINTA - SUINA 08/01/2026</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #03 SUÍNA</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="3" t="n">
         <v>106032</v>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>TOUCINHO FRESCO KG</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="10" t="n">
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="6" t="n">
         <v>17.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E67FC7-BB1D-4E06-A42F-A1E670A957F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFE48B2-83A8-49E7-B1B5-AA9EB3E40031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -130,7 +125,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,28 +138,40 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -216,22 +223,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,393 +549,393 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="35.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>302944</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>5.79</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>325998</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>33.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>298984</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105853</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>320121</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>291441</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>152232</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>239334</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>105457</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>105471</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>105449</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>107260</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>32.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>173342</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>340773</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>1.19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>305039</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>203856</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>167157</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>28.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>203273</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>24.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>289790</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>272499</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>23.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49096881-E82C-42FB-ACE5-1DD78492C724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8192E6A4-5089-4F29-9594-191DB56D252A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -157,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,21 +172,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -235,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -243,22 +248,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,507 +580,507 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="39" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>312226</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="7">
         <v>26.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>127336</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>246975</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>206159</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>109759</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>146742</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>289785</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="11"/>
       <c r="F9" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>147352</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="11"/>
       <c r="F10" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>108770</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="7">
         <v>23.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>225767</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>298984</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>289794</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="7">
         <v>24.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>291441</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>157014</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="7">
         <v>14.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>105458</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>105449</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>106053</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>105062</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="11"/>
       <c r="F20" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>105433</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="11"/>
       <c r="F21" s="7">
         <v>22.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>106054</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>258810</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="11"/>
       <c r="F23" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>106052</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>106050</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="11"/>
       <c r="F25" s="7">
         <v>9.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>106034</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>304309</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="11"/>
       <c r="F27" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>305039</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="11"/>
       <c r="F28" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - QUINTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEC70FC-55F8-4382-BB69-61B1F2B08E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EBCCE0-8E17-4896-9C8F-D88791664F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -100,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,31 +105,30 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -183,25 +177,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,17 +500,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,222 +527,222 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>105471</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>105449</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>105474</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>106053</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>105062</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>105433</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>106054</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>258810</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>106052</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>106050</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="7">
         <v>9.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>106034</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>305039</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="7">
         <v>18.989999999999998</v>
       </c>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D425CE0-3EF1-4723-A93C-A36CA3B555EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EF0002-1DD4-47BB-99A9-7D707D434CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -151,23 +151,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="7"/>
       <color rgb="FFFFFFFF"/>
@@ -175,15 +158,37 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -233,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -241,34 +246,38 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,339 +584,339 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="41.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>139140</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="10">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>21.89</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>259526</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="10">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>14.39</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>309333</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="10">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>302944</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="10">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>6.59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>220822</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="10">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>14.89</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>289786</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="10">
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
         <v>15.19</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>108856</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="10">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>23.89</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>108786</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="10">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>24.19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>289794</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="10">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>29.49</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="10">
         <v>105470</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="12">
         <v>25.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="10">
         <v>105435</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="12">
         <v>42.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <v>106053</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="12">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="10">
         <v>105062</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="12">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="10">
         <v>106034</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="12">
         <v>10.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>106032</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="10">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>343470</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="10">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>139.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>292399</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="10">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>10.19</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0C210-55B2-4C54-9299-9467098B63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC288C0-1E1A-4B91-9937-6BCAC3208FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,7 +40,7 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>PROMOÇAO QUARTA   E  QUINTA  DOS PERECIVEIS</t>
+    <t>QUARTA E QUINTA DOS PERECIVEIS</t>
   </si>
   <si>
     <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
@@ -52,10 +52,19 @@
     <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
   </si>
   <si>
-    <t>MANTEIGA AMANDA 500G</t>
-  </si>
-  <si>
-    <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
+    <t>MANTEIGA QUEIJOLEITE 200G PRIMEIRA QUALIDADE</t>
+  </si>
+  <si>
+    <t>MARGARINA DORIANA 500G CREMOSA</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+  </si>
+  <si>
+    <t>QUEIJO MUSSARELA DEALE 150G FATIADO ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #01 AVES</t>
@@ -73,21 +82,18 @@
     <t>FRANGO MARINGA KG CONGELADO</t>
   </si>
   <si>
-    <t>FRANGO SADIA PCT 1KG CONGELADO A PASSARINHO TEMPERADO</t>
-  </si>
-  <si>
-    <t>PEITO DE FRANGO SADIA 1KG A PASSARINHO</t>
-  </si>
-  <si>
-    <t>AÇOUGUE do  QUINTA 16/07</t>
+    <t>GALINHA SOMAVE KG CONGELADA</t>
+  </si>
+  <si>
+    <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
+  </si>
+  <si>
+    <t>QUINTA DO SUINO 23/07</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #02 BOVINA</t>
   </si>
   <si>
-    <t>ACEM BOVINO KG</t>
-  </si>
-  <si>
     <t>CARNE MOIDA KG</t>
   </si>
   <si>
@@ -112,16 +118,10 @@
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
-    <t>EMPANADO DE FRANGO SEARA 300G CHICKEN SUPREME</t>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
     <t>LINGUIÇA MISTA FRICÓ KG</t>
-  </si>
-  <si>
-    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
   </si>
 </sst>
 </file>
@@ -131,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,31 +151,21 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -219,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -227,26 +217,22 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,400 +535,385 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="85.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>193650</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8">
-        <v>9.49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5">
-        <v>207566</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="3">
+        <v>336816</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
+        <v>11.19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5">
-        <v>276943</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="3">
+        <v>146752</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8">
-        <v>15.59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="5"/>
+      <c r="F4" s="7">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3">
+        <v>309333</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7">
+        <v>13.69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
+        <v>302944</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="3">
         <v>108785</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8">
-        <v>18.690000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7">
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3">
         <v>108856</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8">
-        <v>23.89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="D9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3">
         <v>108786</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8">
-        <v>23.19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="C11" s="3">
         <v>105853</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
-        <v>11.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="5">
-        <v>108788</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8">
-        <v>20.190000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="5">
-        <v>302029</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8">
-        <v>21.29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
+        <v>11.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3">
+        <v>343895</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="5">
-        <v>105470</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3">
+        <v>289794</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3">
         <v>105468</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="3">
         <v>105435</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8">
+      <c r="D15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
         <v>42.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3">
         <v>106053</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8">
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3">
         <v>105062</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="C18" s="3">
         <v>106034</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3">
         <v>106032</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8">
+      <c r="D19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="3">
+        <v>305039</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="5">
-        <v>291439</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8">
-        <v>10.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="3">
         <v>189031</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="5">
-        <v>292399</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="5">
-        <v>105770</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8">
-        <v>11.89</v>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>17.89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - QUINTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - QUINTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC0A360-2299-4E1B-B709-890F697ECEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B28C57-4CB0-4A78-8F2D-05DF1E7F8FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -200,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,21 +220,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -278,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -286,28 +296,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,709 +628,709 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="46.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="46.140625" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="85.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>227503</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>201117</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>291953</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>152160</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>104651</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>139140</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>157413</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6">
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
         <v>11.69</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>306945</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>306946</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>173935</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="9">
         <v>12.59</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>294433</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>222974</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>220822</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>338924</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="63" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>313200</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>104602</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>108770</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>23.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>105853</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6">
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>108788</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6">
+      <c r="E21" s="8"/>
+      <c r="F21" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>343895</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6">
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>302029</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6">
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>23.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>157014</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="6">
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>105451</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6">
+      <c r="E25" s="8"/>
+      <c r="F25" s="9">
         <v>42.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>298422</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>22.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>106053</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="6">
+      <c r="E27" s="8"/>
+      <c r="F27" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>105433</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6">
+      <c r="E28" s="8"/>
+      <c r="F28" s="9">
         <v>23.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>106052</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>106034</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6">
+      <c r="E30" s="8"/>
+      <c r="F30" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>296090</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="6">
+      <c r="E31" s="8"/>
+      <c r="F31" s="9">
         <v>47.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>330578</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="6">
+      <c r="E32" s="8"/>
+      <c r="F32" s="9">
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>161207</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6">
+      <c r="E33" s="8"/>
+      <c r="F33" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>146785</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="6">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9">
         <v>28.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>292399</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="6">
+      <c r="E35" s="8"/>
+      <c r="F35" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>331471</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="6">
+      <c r="E36" s="8"/>
+      <c r="F36" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>170705</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="6">
+      <c r="E37" s="8"/>
+      <c r="F37" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>119916</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="6">
+      <c r="E38" s="8"/>
+      <c r="F38" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="6">
         <v>289807</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="6">
+      <c r="E39" s="8"/>
+      <c r="F39" s="9">
         <v>9.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - QUINTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
